--- a/source_data/Figure4.xlsx
+++ b/source_data/Figure4.xlsx
@@ -621,13 +621,13 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>761.6208923809667</v>
+        <v>760.7249254466265</v>
       </c>
       <c r="D2">
-        <v>0.3273313565120917</v>
+        <v>0.3277605982144325</v>
       </c>
       <c r="E2">
-        <v>-0.7172754342117936</v>
+        <v>-0.7166014610510694</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -638,13 +638,13 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>366.3319961252419</v>
+        <v>367.2606063018525</v>
       </c>
       <c r="D3">
-        <v>-0.4770108338322179</v>
+        <v>-0.4742517082326096</v>
       </c>
       <c r="E3">
-        <v>-0.581045121022629</v>
+        <v>-0.5799335004185945</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -655,13 +655,13 @@
         <v>21</v>
       </c>
       <c r="C4">
-        <v>224.7380761411263</v>
+        <v>224.353388997563</v>
       </c>
       <c r="D4">
-        <v>-0.7651291311541379</v>
+        <v>-0.7655445685541329</v>
       </c>
       <c r="E4">
-        <v>-0.7521368070510666</v>
+        <v>-0.752454713225171</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -672,13 +672,13 @@
         <v>22</v>
       </c>
       <c r="C5">
-        <v>129.4391267822657</v>
+        <v>129.5997411597099</v>
       </c>
       <c r="D5">
-        <v>-0.9590454449967311</v>
+        <v>-0.9586842967304654</v>
       </c>
       <c r="E5">
-        <v>-0.4600000739100291</v>
+        <v>-0.4593124820620898</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -689,13 +689,13 @@
         <v>23</v>
       </c>
       <c r="C6">
-        <v>396.9867302289278</v>
+        <v>397.3376949619366</v>
       </c>
       <c r="D6">
-        <v>-0.4146339337802878</v>
+        <v>-0.4129445093996437</v>
       </c>
       <c r="E6">
-        <v>-0.1691887140149334</v>
+        <v>-0.1668366176234292</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -706,13 +706,13 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>268.3271256090866</v>
+        <v>268.3843488563369</v>
       </c>
       <c r="D7">
-        <v>-0.6764332131655793</v>
+        <v>-0.6757946981003932</v>
       </c>
       <c r="E7">
-        <v>-0.4549903936079426</v>
+        <v>-0.4531484815268795</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -723,13 +723,13 @@
         <v>25</v>
       </c>
       <c r="C8">
-        <v>1693.713085159807</v>
+        <v>1693.572377630412</v>
       </c>
       <c r="D8">
-        <v>2.22397222612444</v>
+        <v>2.229216715799223</v>
       </c>
       <c r="E8">
-        <v>0.9116149081224756</v>
+        <v>0.91467627652231</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -740,13 +740,13 @@
         <v>26</v>
       </c>
       <c r="C9">
-        <v>1129.496421154182</v>
+        <v>1105.442682633964</v>
       </c>
       <c r="D9">
-        <v>1.075892248027986</v>
+        <v>1.030411054845399</v>
       </c>
       <c r="E9">
-        <v>0.7721050530739659</v>
+        <v>0.7754105987172741</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -757,13 +757,13 @@
         <v>27</v>
       </c>
       <c r="C10">
-        <v>1782.370173642894</v>
+        <v>1783.747283001748</v>
       </c>
       <c r="D10">
-        <v>2.404373541252457</v>
+        <v>2.413023430465766</v>
       </c>
       <c r="E10">
-        <v>1.094824542691903</v>
+        <v>1.097491238354519</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -774,13 +774,13 @@
         <v>28</v>
       </c>
       <c r="C11">
-        <v>115.6159125568454</v>
+        <v>115.9169175023088</v>
       </c>
       <c r="D11">
-        <v>-0.9871732130999874</v>
+        <v>-0.9865744825141034</v>
       </c>
       <c r="E11">
-        <v>-0.6112362684879019</v>
+        <v>-0.6112310727908173</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -791,13 +791,13 @@
         <v>29</v>
       </c>
       <c r="C12">
-        <v>657.6704961572924</v>
+        <v>657.7101841964064</v>
       </c>
       <c r="D12">
-        <v>0.1158108959636173</v>
+        <v>0.1177819897151576</v>
       </c>
       <c r="E12">
-        <v>0.9089735022948784</v>
+        <v>0.9117965322096359</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -808,13 +808,13 @@
         <v>30</v>
       </c>
       <c r="C13">
-        <v>935.8299155109588</v>
+        <v>935.9543755315033</v>
       </c>
       <c r="D13">
-        <v>0.6818155541948671</v>
+        <v>0.684937014427942</v>
       </c>
       <c r="E13">
-        <v>0.9667512081131547</v>
+        <v>0.9709374070738784</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -825,13 +825,13 @@
         <v>31</v>
       </c>
       <c r="C14">
-        <v>1538.67095069796</v>
+        <v>1538.9896816228</v>
       </c>
       <c r="D14">
-        <v>1.908489218101816</v>
+        <v>1.914125312260165</v>
       </c>
       <c r="E14">
-        <v>1.169387154065749</v>
+        <v>1.163861335207403</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -842,13 +842,13 @@
         <v>32</v>
       </c>
       <c r="C15">
-        <v>105.8284781199683</v>
+        <v>106.0508645065856</v>
       </c>
       <c r="D15">
-        <v>-1.007088891297323</v>
+        <v>-1.006684809000194</v>
       </c>
       <c r="E15">
-        <v>-0.5643503473309036</v>
+        <v>-0.5648178640984415</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -859,13 +859,13 @@
         <v>33</v>
       </c>
       <c r="C16">
-        <v>357.9410575011049</v>
+        <v>358.2471900781778</v>
       </c>
       <c r="D16">
-        <v>-0.4940848928708427</v>
+        <v>-0.492624074881329</v>
       </c>
       <c r="E16">
-        <v>-0.577630309214904</v>
+        <v>-0.5762590270888506</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -876,13 +876,13 @@
         <v>34</v>
       </c>
       <c r="C17">
-        <v>1212.045814592163</v>
+        <v>1212.290285512076</v>
       </c>
       <c r="D17">
-        <v>1.243865496349498</v>
+        <v>1.248202321430571</v>
       </c>
       <c r="E17">
-        <v>0.7337618626528613</v>
+        <v>0.7373168665748238</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -893,13 +893,13 @@
         <v>35</v>
       </c>
       <c r="C18">
-        <v>264.4868870666639</v>
+        <v>264.7755914388144</v>
       </c>
       <c r="D18">
-        <v>-0.6842474116161692</v>
+        <v>-0.6831505566090528</v>
       </c>
       <c r="E18">
-        <v>-0.5395978054658387</v>
+        <v>-0.5381537307433059</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -910,13 +910,13 @@
         <v>36</v>
       </c>
       <c r="C19">
-        <v>315.147738113812</v>
+        <v>315.742931686186</v>
       </c>
       <c r="D19">
-        <v>-0.5811616424940123</v>
+        <v>-0.5792620154724288</v>
       </c>
       <c r="E19">
-        <v>-0.5739475911056899</v>
+        <v>-0.5739455062790422</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -927,13 +927,13 @@
         <v>37</v>
       </c>
       <c r="C20">
-        <v>581.861334118146</v>
+        <v>582.0425431565758</v>
       </c>
       <c r="D20">
-        <v>-0.03844718722647074</v>
+        <v>-0.0364540524389775</v>
       </c>
       <c r="E20">
-        <v>-0.6687578503437784</v>
+        <v>-0.6674930315773209</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -944,13 +944,13 @@
         <v>38</v>
       </c>
       <c r="C21">
-        <v>361.3806737189068</v>
+        <v>360.9791588770014</v>
       </c>
       <c r="D21">
-        <v>-0.4870858891832187</v>
+        <v>-0.4870554057774867</v>
       </c>
       <c r="E21">
-        <v>0.4741978027127218</v>
+        <v>0.4770067340971512</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -961,13 +961,13 @@
         <v>39</v>
       </c>
       <c r="C22">
-        <v>293.8994321615687</v>
+        <v>293.9001375395331</v>
       </c>
       <c r="D22">
-        <v>-0.6243981439809571</v>
+        <v>-0.6237849591306547</v>
       </c>
       <c r="E22">
-        <v>1.443863017501712</v>
+        <v>1.438479167678528</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -978,13 +978,13 @@
         <v>40</v>
       </c>
       <c r="C23">
-        <v>277.3645721203505</v>
+        <v>277.6387050865425</v>
       </c>
       <c r="D23">
-        <v>-0.6580436262309468</v>
+        <v>-0.6569312148727341</v>
       </c>
       <c r="E23">
-        <v>-0.1682353059246957</v>
+        <v>-0.1669779006746255</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -995,13 +995,13 @@
         <v>41</v>
       </c>
       <c r="C24">
-        <v>70.97469521067249</v>
+        <v>70.82400226177489</v>
       </c>
       <c r="D24">
-        <v>-1.078010104497584</v>
+        <v>-1.078488974367111</v>
       </c>
       <c r="E24">
-        <v>-0.6123951474334095</v>
+        <v>-0.6120168581886187</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1012,13 +1012,13 @@
         <v>42</v>
       </c>
       <c r="C25">
-        <v>749.4718399140905</v>
+        <v>749.675842484855</v>
       </c>
       <c r="D25">
-        <v>0.3026102080953821</v>
+        <v>0.305238859700617</v>
       </c>
       <c r="E25">
-        <v>0.3162585832570017</v>
+        <v>0.3185478810015305</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1029,13 +1029,13 @@
         <v>43</v>
       </c>
       <c r="C26">
-        <v>977.7404030340294</v>
+        <v>977.9020420680006</v>
       </c>
       <c r="D26">
-        <v>0.7670958989048186</v>
+        <v>0.7704404340572806</v>
       </c>
       <c r="E26">
-        <v>1.046988063963639</v>
+        <v>1.051360992945293</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1046,13 +1046,13 @@
         <v>44</v>
       </c>
       <c r="C27">
-        <v>103.4086049849635</v>
+        <v>103.6178445452273</v>
       </c>
       <c r="D27">
-        <v>-1.012012900234083</v>
+        <v>-1.01164412006322</v>
       </c>
       <c r="E27">
-        <v>-0.4216848518651977</v>
+        <v>-0.4198849803123225</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1063,13 +1063,13 @@
         <v>45</v>
       </c>
       <c r="C28">
-        <v>548.0485353772867</v>
+        <v>545.3414059931569</v>
       </c>
       <c r="D28">
-        <v>-0.1072501838664256</v>
+        <v>-0.1112632847720177</v>
       </c>
       <c r="E28">
-        <v>0.529075395600522</v>
+        <v>0.5326918277757626</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1080,13 +1080,13 @@
         <v>19</v>
       </c>
       <c r="C29">
-        <v>67.25001813808062</v>
+        <v>18.1468302912281</v>
       </c>
       <c r="D29">
-        <v>-0.6078556065182849</v>
+        <v>-0.9031548211455904</v>
       </c>
       <c r="E29">
-        <v>-0.08742563309279472</v>
+        <v>-0.07312191914846025</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1097,13 +1097,13 @@
         <v>20</v>
       </c>
       <c r="C30">
-        <v>135.6988243144004</v>
+        <v>113.6830247105905</v>
       </c>
       <c r="D30">
-        <v>-0.006173291023570555</v>
+        <v>0.5542055813404465</v>
       </c>
       <c r="E30">
-        <v>0.784224579192383</v>
+        <v>1.08278494160141</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1114,13 +1114,13 @@
         <v>21</v>
       </c>
       <c r="C31">
-        <v>52.32549498306765</v>
+        <v>14.88354558446479</v>
       </c>
       <c r="D31">
-        <v>-0.7390459391360844</v>
+        <v>-0.9529347181006573</v>
       </c>
       <c r="E31">
-        <v>-0.1535659759551434</v>
+        <v>-0.2983393609807263</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1131,13 +1131,13 @@
         <v>22</v>
       </c>
       <c r="C32">
-        <v>10.89184498677155</v>
+        <v>4.173783617492655</v>
       </c>
       <c r="D32">
-        <v>-1.103258200266705</v>
+        <v>-1.116307177152186</v>
       </c>
       <c r="E32">
-        <v>0.01165488565688923</v>
+        <v>-0.03049144794714115</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1148,13 +1148,13 @@
         <v>23</v>
       </c>
       <c r="C33">
-        <v>153.3787802251116</v>
+        <v>123.0875237166268</v>
       </c>
       <c r="D33">
-        <v>0.1492379923054483</v>
+        <v>0.6976668583979596</v>
       </c>
       <c r="E33">
-        <v>0.1875234819687346</v>
+        <v>0.4630155635761885</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1165,13 +1165,13 @@
         <v>24</v>
       </c>
       <c r="C34">
-        <v>324.9365537246113</v>
+        <v>214.9518090430962</v>
       </c>
       <c r="D34">
-        <v>1.657274204571883</v>
+        <v>2.099013988154912</v>
       </c>
       <c r="E34">
-        <v>0.3246899013133759</v>
+        <v>0.7204227012975959</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1182,13 +1182,13 @@
         <v>25</v>
       </c>
       <c r="C35">
-        <v>27.21449156777539</v>
+        <v>12.59228926670447</v>
       </c>
       <c r="D35">
-        <v>-0.9597780091796332</v>
+        <v>-0.9878867721336271</v>
       </c>
       <c r="E35">
-        <v>-0.003162391410043042</v>
+        <v>0.1061510272786047</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1199,13 +1199,13 @@
         <v>26</v>
       </c>
       <c r="C36">
-        <v>170.6191924335079</v>
+        <v>74.47665136494027</v>
       </c>
       <c r="D36">
-        <v>0.3007855753401389</v>
+        <v>-0.04386948734215595</v>
       </c>
       <c r="E36">
-        <v>-0.3035764142299998</v>
+        <v>0.008010169954639899</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1216,13 +1216,13 @@
         <v>27</v>
       </c>
       <c r="C37">
-        <v>62.71252183793935</v>
+        <v>47.19195464795877</v>
       </c>
       <c r="D37">
-        <v>-0.6477413464300235</v>
+        <v>-0.4600849000539551</v>
       </c>
       <c r="E37">
-        <v>0.5409349372115764</v>
+        <v>-0.02618520710279744</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1233,13 +1233,13 @@
         <v>28</v>
       </c>
       <c r="C38">
-        <v>51.40529400277442</v>
+        <v>36.89137490555263</v>
       </c>
       <c r="D38">
-        <v>-0.7471347384515483</v>
+        <v>-0.6172154737644578</v>
       </c>
       <c r="E38">
-        <v>0.4066903086548246</v>
+        <v>0.3605095954339011</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1250,13 +1250,13 @@
         <v>29</v>
       </c>
       <c r="C39">
-        <v>294.4720208791497</v>
+        <v>227.7820589871915</v>
       </c>
       <c r="D39">
-        <v>1.389483257046733</v>
+        <v>2.294733509286827</v>
       </c>
       <c r="E39">
-        <v>0.4701337057896402</v>
+        <v>-0.2646850339426755</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1267,13 +1267,13 @@
         <v>30</v>
       </c>
       <c r="C40">
-        <v>498.3658184716266</v>
+        <v>114.3111642140532</v>
       </c>
       <c r="D40">
-        <v>3.181761298163154</v>
+        <v>0.5637875585706209</v>
       </c>
       <c r="E40">
-        <v>-0.4669870757719924</v>
+        <v>-0.2752432602339528</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1284,13 +1284,13 @@
         <v>31</v>
       </c>
       <c r="C41">
-        <v>196.5821881713077</v>
+        <v>155.9401117997334</v>
       </c>
       <c r="D41">
-        <v>0.5290068733487383</v>
+        <v>1.198817875376304</v>
       </c>
       <c r="E41">
-        <v>-0.5086165415788141</v>
+        <v>-0.472077654279435</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1301,13 +1301,13 @@
         <v>32</v>
       </c>
       <c r="C42">
-        <v>57.78838556090096</v>
+        <v>28.80723400106806</v>
       </c>
       <c r="D42">
-        <v>-0.6910257495114751</v>
+        <v>-0.7405352994485098</v>
       </c>
       <c r="E42">
-        <v>0.1876736803076176</v>
+        <v>0.1226422507039214</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1318,13 +1318,13 @@
         <v>33</v>
       </c>
       <c r="C43">
-        <v>177.5011666846259</v>
+        <v>131.1837535976336</v>
       </c>
       <c r="D43">
-        <v>0.3612798693081203</v>
+        <v>0.8211710958203821</v>
       </c>
       <c r="E43">
-        <v>0.7107339471260448</v>
+        <v>1.029391838705423</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1335,13 +1335,13 @@
         <v>34</v>
       </c>
       <c r="C44">
-        <v>20.45328340547615</v>
+        <v>9.357281171826848</v>
       </c>
       <c r="D44">
-        <v>-1.019210738687797</v>
+        <v>-1.037235322469445</v>
       </c>
       <c r="E44">
-        <v>-0.1345756128919413</v>
+        <v>-0.6448239917049452</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1352,13 +1352,13 @@
         <v>35</v>
       </c>
       <c r="C45">
-        <v>194.4231476852588</v>
+        <v>99.65401283102314</v>
       </c>
       <c r="D45">
-        <v>0.5100283615022873</v>
+        <v>0.3401995020367059</v>
       </c>
       <c r="E45">
-        <v>0.6809842486872114</v>
+        <v>1.125586157462158</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1369,13 +1369,13 @@
         <v>36</v>
       </c>
       <c r="C46">
-        <v>94.90797018994768</v>
+        <v>75.87266356128049</v>
       </c>
       <c r="D46">
-        <v>-0.3647352138916814</v>
+        <v>-0.02257396778855866</v>
       </c>
       <c r="E46">
-        <v>0.4982631521062359</v>
+        <v>0.5292217258080152</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1386,13 +1386,13 @@
         <v>37</v>
       </c>
       <c r="C47">
-        <v>264.1619171688866</v>
+        <v>202.5028770043829</v>
       </c>
       <c r="D47">
-        <v>1.123049780671724</v>
+        <v>1.909111295079003</v>
       </c>
       <c r="E47">
-        <v>0.558379964853324</v>
+        <v>0.8118037988536985</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1403,13 +1403,13 @@
         <v>38</v>
       </c>
       <c r="C48">
-        <v>5.639064915764338</v>
+        <v>1.690204324382488</v>
       </c>
       <c r="D48">
-        <v>-1.149431465403964</v>
+        <v>-1.154193029108201</v>
       </c>
       <c r="E48">
-        <v>-0.03260790041211643</v>
+        <v>-0.4967072024314423</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1420,13 +1420,13 @@
         <v>39</v>
       </c>
       <c r="C49">
-        <v>105.898746505972</v>
+        <v>88.07331630847186</v>
       </c>
       <c r="D49">
-        <v>-0.2681235107470655</v>
+        <v>0.1635413396748036</v>
       </c>
       <c r="E49">
-        <v>-0.4234843432112081</v>
+        <v>-0.3804524316222331</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1437,13 +1437,13 @@
         <v>40</v>
       </c>
       <c r="C50">
-        <v>119.8505813666094</v>
+        <v>40.26942982855918</v>
       </c>
       <c r="D50">
-        <v>-0.145483354208406</v>
+        <v>-0.5656848103113719</v>
       </c>
       <c r="E50">
-        <v>0.4338209997826846</v>
+        <v>0.0197047540222324</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1454,13 +1454,13 @@
         <v>41</v>
       </c>
       <c r="C51">
-        <v>149.2739937838233</v>
+        <v>61.76264161675046</v>
       </c>
       <c r="D51">
-        <v>0.1131558814758794</v>
+        <v>-0.2378158181170609</v>
       </c>
       <c r="E51">
-        <v>-0.657333769928191</v>
+        <v>-0.8557233652316631</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1471,13 +1471,13 @@
         <v>42</v>
       </c>
       <c r="C52">
-        <v>12.4864596753001</v>
+        <v>2.519589890469162</v>
       </c>
       <c r="D52">
-        <v>-1.089241133911387</v>
+        <v>-1.14154113639095</v>
       </c>
       <c r="E52">
-        <v>-0.04464596671063179</v>
+        <v>-0.4992375809748925</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1488,13 +1488,13 @@
         <v>43</v>
       </c>
       <c r="C53">
-        <v>26.25349444801241</v>
+        <v>9.69468052802868</v>
       </c>
       <c r="D53">
-        <v>-0.968225416877487</v>
+        <v>-1.03208845154224</v>
       </c>
       <c r="E53">
-        <v>-0.499061971285507</v>
+        <v>-0.2553004287726487</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1505,13 +1505,13 @@
         <v>44</v>
       </c>
       <c r="C54">
-        <v>167.0590109613497</v>
+        <v>93.37583632616321</v>
       </c>
       <c r="D54">
-        <v>0.2694906799078993</v>
+        <v>0.2444288269160451</v>
       </c>
       <c r="E54">
-        <v>0.4274845425528019</v>
+        <v>0.8644708665348996</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1522,13 +1522,13 @@
         <v>45</v>
       </c>
       <c r="C55">
-        <v>241.2797722684294</v>
+        <v>85.64141124851885</v>
       </c>
       <c r="D55">
-        <v>0.9219099406031086</v>
+        <v>0.1264437542149557</v>
       </c>
       <c r="E55">
-        <v>-0.5140302631294876</v>
+        <v>-0.2780188510685278</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1539,13 +1539,13 @@
         <v>19</v>
       </c>
       <c r="C56">
-        <v>72.13933769774226</v>
+        <v>10.65360682863999</v>
       </c>
       <c r="D56">
-        <v>1.11781961987026</v>
+        <v>-0.2475230540269726</v>
       </c>
       <c r="E56">
-        <v>0.2777014833966183</v>
+        <v>0.4424316044307555</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1556,13 +1556,13 @@
         <v>20</v>
       </c>
       <c r="C57">
-        <v>37.11232094043599</v>
+        <v>24.91581898666</v>
       </c>
       <c r="D57">
-        <v>-0.01054249041357683</v>
+        <v>0.6218109375513773</v>
       </c>
       <c r="E57">
-        <v>-0.0462622701462853</v>
+        <v>-0.07739947787258455</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1573,13 +1573,13 @@
         <v>21</v>
       </c>
       <c r="C58">
-        <v>28.90000634733787</v>
+        <v>9.990325118339383</v>
       </c>
       <c r="D58">
-        <v>-0.2750944129706145</v>
+        <v>-0.2879525000601602</v>
       </c>
       <c r="E58">
-        <v>0.2002258877968467</v>
+        <v>-0.2899668849147384</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1590,13 +1590,13 @@
         <v>22</v>
       </c>
       <c r="C59">
-        <v>19.81032332703572</v>
+        <v>13.52957110361621</v>
       </c>
       <c r="D59">
-        <v>-0.5679099269398395</v>
+        <v>-0.0722225133323859</v>
       </c>
       <c r="E59">
-        <v>0.6148473927586382</v>
+        <v>0.4073714962918382</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1607,13 +1607,13 @@
         <v>23</v>
       </c>
       <c r="C60">
-        <v>53.95343031697146</v>
+        <v>41.34335787242581</v>
       </c>
       <c r="D60">
-        <v>0.5319778688649413</v>
+        <v>1.623129512337882</v>
       </c>
       <c r="E60">
-        <v>-0.5046259082555266</v>
+        <v>-0.395963661815703</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1624,13 +1624,13 @@
         <v>24</v>
       </c>
       <c r="C61">
-        <v>26.80010861770792</v>
+        <v>7.645624680572847</v>
       </c>
       <c r="D61">
-        <v>-0.3427406258925655</v>
+        <v>-0.4308705669094802</v>
       </c>
       <c r="E61">
-        <v>-0.1090211041038474</v>
+        <v>0.09448187291392954</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1641,13 +1641,13 @@
         <v>25</v>
       </c>
       <c r="C62">
-        <v>15.91224391933893</v>
+        <v>2.618608506616466</v>
       </c>
       <c r="D62">
-        <v>-0.6934828564587443</v>
+        <v>-0.7372855877922662</v>
       </c>
       <c r="E62">
-        <v>0.3487798281504833</v>
+        <v>0.2529207028590955</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1658,13 +1658,13 @@
         <v>26</v>
       </c>
       <c r="C63">
-        <v>67.56294097297004</v>
+        <v>12.99472341907263</v>
       </c>
       <c r="D63">
-        <v>0.9703953415870431</v>
+        <v>-0.1048234357796972</v>
       </c>
       <c r="E63">
-        <v>-0.3066604893615237</v>
+        <v>0.2608387898268477</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1675,13 +1675,13 @@
         <v>27</v>
       </c>
       <c r="C64">
-        <v>31.53903856718597</v>
+        <v>20.79026595101068</v>
       </c>
       <c r="D64">
-        <v>-0.1900804939912395</v>
+        <v>0.3703433918289961</v>
       </c>
       <c r="E64">
-        <v>0.23071386127757</v>
+        <v>-0.3579793564163223</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1692,13 +1692,13 @@
         <v>28</v>
       </c>
       <c r="C65">
-        <v>19.45962174161331</v>
+        <v>9.261991768428196</v>
       </c>
       <c r="D65">
-        <v>-0.5792074457593541</v>
+        <v>-0.3323470814380482</v>
       </c>
       <c r="E65">
-        <v>0.1418283100583047</v>
+        <v>-0.3789376167722067</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1709,13 +1709,13 @@
         <v>29</v>
       </c>
       <c r="C66">
-        <v>98.44700785630522</v>
+        <v>72.69112413964704</v>
       </c>
       <c r="D66">
-        <v>1.965296252620474</v>
+        <v>3.533890513100606</v>
       </c>
       <c r="E66">
-        <v>0.6742124764848908</v>
+        <v>-0.09687737099560176</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1726,13 +1726,13 @@
         <v>30</v>
       </c>
       <c r="C67">
-        <v>51.25499690888518</v>
+        <v>9.403169138378297</v>
       </c>
       <c r="D67">
-        <v>0.44505039696788</v>
+        <v>-0.3237418044179444</v>
       </c>
       <c r="E67">
-        <v>-0.2864030479032627</v>
+        <v>0.2713906916793039</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1743,13 +1743,13 @@
         <v>31</v>
       </c>
       <c r="C68">
-        <v>13.80639958278007</v>
+        <v>6.939301534230723</v>
       </c>
       <c r="D68">
-        <v>-0.7613206336806136</v>
+        <v>-0.4739235458829062</v>
       </c>
       <c r="E68">
-        <v>-0.1047289668792284</v>
+        <v>0.08410158774571222</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1760,13 +1760,13 @@
         <v>32</v>
       </c>
       <c r="C69">
-        <v>13.81219038420153</v>
+        <v>6.937813763268943</v>
       </c>
       <c r="D69">
-        <v>-0.7611340885072856</v>
+        <v>-0.4740142309641845</v>
       </c>
       <c r="E69">
-        <v>0.8919436630906452</v>
+        <v>0.608959200599108</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1777,13 +1777,13 @@
         <v>33</v>
       </c>
       <c r="C70">
-        <v>31.85785010194586</v>
+        <v>15.4782711480731</v>
       </c>
       <c r="D70">
-        <v>-0.179810282895701</v>
+        <v>0.04655788127028416</v>
       </c>
       <c r="E70">
-        <v>-0.01240871164986046</v>
+        <v>0.03765113338363407</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1794,13 +1794,13 @@
         <v>34</v>
       </c>
       <c r="C71">
-        <v>4.702669778896399</v>
+        <v>0.6524448268638271</v>
       </c>
       <c r="D71">
-        <v>-1.05458865145496</v>
+        <v>-0.8571304548351801</v>
       </c>
       <c r="E71">
-        <v>-0.6056288620182403</v>
+        <v>-0.5029309234413821</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1811,13 +1811,13 @@
         <v>35</v>
       </c>
       <c r="C72">
-        <v>25.55803571858191</v>
+        <v>2.055254347076264</v>
       </c>
       <c r="D72">
-        <v>-0.382752825826545</v>
+        <v>-0.7716240841460703</v>
       </c>
       <c r="E72">
-        <v>0.02817979693630834</v>
+        <v>0.201287526466905</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1828,13 +1828,13 @@
         <v>36</v>
       </c>
       <c r="C73">
-        <v>6.172081461636783</v>
+        <v>2.005149077662273</v>
       </c>
       <c r="D73">
-        <v>-1.007252948311848</v>
+        <v>-0.7746781835646013</v>
       </c>
       <c r="E73">
-        <v>0.4860598020432489</v>
+        <v>0.1289573523135173</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1845,13 +1845,13 @@
         <v>37</v>
       </c>
       <c r="C74">
-        <v>69.57627624060105</v>
+        <v>36.86804480404135</v>
       </c>
       <c r="D74">
-        <v>1.035253026928434</v>
+        <v>1.350342813458658</v>
       </c>
       <c r="E74">
-        <v>-0.2554213736146875</v>
+        <v>-0.2231058530540407</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1862,13 +1862,13 @@
         <v>38</v>
       </c>
       <c r="C75">
-        <v>2.347076112238387</v>
+        <v>0.4231598468599666</v>
       </c>
       <c r="D75">
-        <v>-1.130471866377255</v>
+        <v>-0.8711062129200599</v>
       </c>
       <c r="E75">
-        <v>-0.4665915574880859</v>
+        <v>-0.2334607709535403</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1879,13 +1879,13 @@
         <v>39</v>
       </c>
       <c r="C76">
-        <v>50.76367145760086</v>
+        <v>42.66549156340798</v>
       </c>
       <c r="D76">
-        <v>0.4292228137372385</v>
+        <v>1.703718396183326</v>
       </c>
       <c r="E76">
-        <v>-0.515739287855543</v>
+        <v>-0.5969215700003695</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1896,13 +1896,13 @@
         <v>40</v>
       </c>
       <c r="C77">
-        <v>56.26842720480796</v>
+        <v>8.969068329768112</v>
       </c>
       <c r="D77">
-        <v>0.6065532970767897</v>
+        <v>-0.3502018363200973</v>
       </c>
       <c r="E77">
-        <v>0.4398244508022977</v>
+        <v>0.4832777820718237</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1913,13 +1913,13 @@
         <v>41</v>
       </c>
       <c r="C78">
-        <v>41.96251417765986</v>
+        <v>7.737114786834848</v>
       </c>
       <c r="D78">
-        <v>0.1457018827329532</v>
+        <v>-0.4252939103301606</v>
       </c>
       <c r="E78">
-        <v>0.02404689770586204</v>
+        <v>-0.2863828269407601</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1930,13 +1930,13 @@
         <v>42</v>
       </c>
       <c r="C79">
-        <v>2.891222480621525</v>
+        <v>0.2984921335798238</v>
       </c>
       <c r="D79">
-        <v>-1.112942707420147</v>
+        <v>-0.8787051659861049</v>
       </c>
       <c r="E79">
-        <v>-0.4700973892795073</v>
+        <v>-0.2319409803403312</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1947,13 +1947,13 @@
         <v>43</v>
       </c>
       <c r="C80">
-        <v>5.164859774939202</v>
+        <v>1.40195898533738</v>
       </c>
       <c r="D80">
-        <v>-1.03969963927044</v>
+        <v>-0.8114448257117974</v>
       </c>
       <c r="E80">
-        <v>-0.5379419345619445</v>
+        <v>-0.02713947573837393</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1964,13 +1964,13 @@
         <v>44</v>
       </c>
       <c r="C81">
-        <v>26.22520367785448</v>
+        <v>5.175996558062884</v>
       </c>
       <c r="D81">
-        <v>-0.3612606430450488</v>
+        <v>-0.5814034330363143</v>
       </c>
       <c r="E81">
-        <v>0.1988250593315105</v>
+        <v>0.5740434120944263</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1981,13 +1981,13 @@
         <v>45</v>
       </c>
       <c r="C82">
-        <v>136.8689306232771</v>
+        <v>23.84431714789717</v>
       </c>
       <c r="D82">
-        <v>3.203022038829768</v>
+        <v>0.5564989817233028</v>
       </c>
       <c r="E82">
-        <v>-0.387609175131249</v>
+        <v>0.02983241027439258</v>
       </c>
     </row>
   </sheetData>
@@ -2031,19 +2031,19 @@
         <v>18</v>
       </c>
       <c r="B2">
-        <v>0.515893824814413</v>
+        <v>0.5159726265648679</v>
       </c>
       <c r="C2">
-        <v>0.09241959529851383</v>
+        <v>0.09372257890731592</v>
       </c>
       <c r="D2">
-        <v>0.5158938248144128</v>
+        <v>0.5159726265648682</v>
       </c>
       <c r="E2">
         <v>0.001</v>
       </c>
       <c r="F2">
-        <v>5.610300263922954</v>
+        <v>5.614456653603256</v>
       </c>
       <c r="G2" t="s">
         <v>55</v>
@@ -2057,19 +2057,19 @@
         <v>46</v>
       </c>
       <c r="B3">
-        <v>0.0042388518958106</v>
+        <v>0.2308366236524081</v>
       </c>
       <c r="C3">
-        <v>0.08867105465168419</v>
+        <v>0.08864102428856102</v>
       </c>
       <c r="D3">
-        <v>0.004238851895810627</v>
+        <v>0.2308366236524081</v>
       </c>
       <c r="E3">
-        <v>0.285</v>
+        <v>0.017</v>
       </c>
       <c r="F3">
-        <v>0.4591902116272888</v>
+        <v>2.689336689284548</v>
       </c>
       <c r="G3" t="s">
         <v>55</v>
@@ -2083,19 +2083,19 @@
         <v>47</v>
       </c>
       <c r="B4">
-        <v>-0.006290288838290196</v>
+        <v>-0.1052665620255537</v>
       </c>
       <c r="C4">
-        <v>-0.001924117348724758</v>
+        <v>0.006612547914642001</v>
       </c>
       <c r="D4">
-        <v>-0.006290288838290217</v>
+        <v>-0.1052665620255537</v>
       </c>
       <c r="E4">
-        <v>0.326</v>
+        <v>0.243</v>
       </c>
       <c r="F4">
-        <v>0.3406099654413746</v>
+        <v>-0.7250507386720375</v>
       </c>
       <c r="G4" t="s">
         <v>55</v>
